--- a/data/trans_bre/P1001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,8</t>
+          <t>-0,06; 4,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 11,76</t>
+          <t>5,03; 11,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,09</t>
+          <t>3,76; 10,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,49</t>
+          <t>2,58; 7,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 143,19</t>
+          <t>-1,78; 140,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,43; 217,99</t>
+          <t>59,08; 218,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,32; 216,92</t>
+          <t>47,79; 220,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,2; 178,78</t>
+          <t>35,2; 184,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,88</t>
+          <t>-0,83; 4,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 10,3</t>
+          <t>4,72; 10,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,95</t>
+          <t>4,62; 9,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,15</t>
+          <t>4,85; 10,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 81,35</t>
+          <t>-12,24; 83,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,18; 152,47</t>
+          <t>47,02; 149,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,24; 241,38</t>
+          <t>78,09; 243,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,76; 419,74</t>
+          <t>85,71; 448,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,67</t>
+          <t>2,64; 9,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,71</t>
+          <t>4,68; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,14</t>
+          <t>4,05; 10,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,23</t>
+          <t>-5,97; 3,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,32; 169,88</t>
+          <t>25,95; 157,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,66; 255,46</t>
+          <t>64,69; 266,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,01; 213,93</t>
+          <t>54,31; 221,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 56,48</t>
+          <t>-57,89; 49,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,41</t>
+          <t>1,4; 6,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,93</t>
+          <t>4,31; 9,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,57</t>
+          <t>1,34; 6,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,79</t>
+          <t>3,26; 9,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 121,26</t>
+          <t>17,05; 124,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,43; 163,79</t>
+          <t>46,24; 161,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 101,11</t>
+          <t>15,45; 109,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,96; 184,41</t>
+          <t>46,89; 194,49</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,69</t>
+          <t>2,14; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,08</t>
+          <t>6,2; 9,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,52</t>
+          <t>4,75; 7,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,69</t>
+          <t>3,01; 6,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 85,8</t>
+          <t>31,87; 86,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,82; 139,57</t>
+          <t>79,9; 142,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,81; 138,51</t>
+          <t>70,94; 138,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,35; 139,21</t>
+          <t>48,89; 143,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,75</t>
+          <t>0,04; 4,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,93</t>
+          <t>5,04; 11,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,02</t>
+          <t>3,57; 9,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,67</t>
+          <t>2,83; 7,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 140,95</t>
+          <t>-2,03; 152,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,08; 218,54</t>
+          <t>59,58; 212,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,79; 220,61</t>
+          <t>44,2; 210,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,2; 184,07</t>
+          <t>37,6; 177,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>169,71%</t>
+          <t>110,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,05</t>
+          <t>-0,74; 4,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 10,6</t>
+          <t>4,49; 10,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,59</t>
+          <t>4,65; 9,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 10,19</t>
+          <t>3,39; 7,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 83,72</t>
+          <t>-9,96; 79,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,02; 149,32</t>
+          <t>44,01; 147,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,09; 243,24</t>
+          <t>75,64; 238,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,71; 448,49</t>
+          <t>52,67; 186,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,21</t>
+          <t>2,69; 9,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,13</t>
+          <t>4,35; 10,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,57</t>
+          <t>4,17; 10,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,95</t>
+          <t>0,7; 7,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,95; 157,6</t>
+          <t>29,34; 156,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,69; 266,32</t>
+          <t>59,03; 266,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,31; 221,59</t>
+          <t>57,21; 223,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,89; 49,49</t>
+          <t>6,12; 111,17</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,3</t>
+          <t>7,23</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>107,97%</t>
+          <t>130,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,48</t>
+          <t>1,58; 6,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,64</t>
+          <t>4,06; 9,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,72</t>
+          <t>1,29; 6,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,04</t>
+          <t>4,91; 9,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 124,98</t>
+          <t>20,2; 116,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 161,2</t>
+          <t>46,15; 155,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 109,11</t>
+          <t>12,79; 99,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,89; 194,49</t>
+          <t>68,81; 208,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,75</t>
+          <t>2,08; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,27</t>
+          <t>6,11; 8,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,49</t>
+          <t>4,64; 7,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,69</t>
+          <t>4,5; 6,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,87; 86,4</t>
+          <t>31,78; 87,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,9; 142,72</t>
+          <t>78,56; 141,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,94; 138,12</t>
+          <t>69,69; 139,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,89; 143,9</t>
+          <t>65,56; 125,88</t>
         </is>
       </c>
     </row>
